--- a/artfynd/A 65332-2020 artfynd.xlsx
+++ b/artfynd/A 65332-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 65332-2020 artfynd.xlsx
+++ b/artfynd/A 65332-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY97"/>
+  <dimension ref="A1:AY96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5492,7 +5492,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>95526602</v>
+        <v>95526559</v>
       </c>
       <c r="B45" t="n">
         <v>73693</v>
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>731263.063338915</v>
+        <v>731141.4169256137</v>
       </c>
       <c r="R45" t="n">
-        <v>7377384.930477669</v>
+        <v>7377260.22102132</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
@@ -5604,10 +5604,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>95526559</v>
+        <v>95525733</v>
       </c>
       <c r="B46" t="n">
-        <v>73693</v>
+        <v>56542</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5620,34 +5620,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>103022</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Görjeån, Ö Skravelstjärnen, Lu lm</t>
+          <t>Görjeån, Ö Skraveltjärnen, Lu lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>731141.4169256137</v>
+        <v>731305.526533796</v>
       </c>
       <c r="R46" t="n">
-        <v>7377260.22102132</v>
+        <v>7377179.383949534</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
@@ -5704,22 +5704,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Astrid Eklund</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Amanda Helander, Astrid Eklund, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Wanyi Ji, Tore Dahlberg, Linnea Backman</t>
+          <t>Astrid Eklund, Amanda Helander, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Karl Soler Kinnerbäck, Linnea Backman, Tore Dahlberg, Wanyi Ji</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>95525733</v>
+        <v>95525707</v>
       </c>
       <c r="B47" t="n">
-        <v>56542</v>
+        <v>95525</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5728,25 +5728,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103022</v>
+        <v>221941</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5756,10 +5756,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>731305.526533796</v>
+        <v>731068.8657165424</v>
       </c>
       <c r="R47" t="n">
-        <v>7377179.383949534</v>
+        <v>7377382.447470394</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
@@ -5828,10 +5828,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>95525707</v>
+        <v>95526557</v>
       </c>
       <c r="B48" t="n">
-        <v>95525</v>
+        <v>73693</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5840,38 +5840,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221941</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Görjeån, Ö Skraveltjärnen, Lu lm</t>
+          <t>Görjeån, Ö Skravelstjärnen, Lu lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>731068.8657165424</v>
+        <v>731081.5441688144</v>
       </c>
       <c r="R48" t="n">
-        <v>7377382.447470394</v>
+        <v>7377336.460497634</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5928,22 +5928,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Astrid Eklund</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Astrid Eklund, Amanda Helander, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Karl Soler Kinnerbäck, Linnea Backman, Tore Dahlberg, Wanyi Ji</t>
+          <t>Karl Soler Kinnerbäck, Amanda Helander, Astrid Eklund, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Wanyi Ji, Tore Dahlberg, Linnea Backman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>95526557</v>
+        <v>95526566</v>
       </c>
       <c r="B49" t="n">
-        <v>73693</v>
+        <v>77588</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5956,21 +5956,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>864</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5980,10 +5980,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>731081.5441688144</v>
+        <v>731105.0736012852</v>
       </c>
       <c r="R49" t="n">
-        <v>7377336.460497634</v>
+        <v>7377382.643747968</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6052,10 +6052,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>95526566</v>
+        <v>95521892</v>
       </c>
       <c r="B50" t="n">
-        <v>77588</v>
+        <v>76909</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6068,34 +6068,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>864</v>
+        <v>6437</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Görjeån, Ö Skravelstjärnen, Lu lm</t>
+          <t>Görjeån, Ö Skraveltjärnen, Lu lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>731105.0736012852</v>
+        <v>731095.7841368329</v>
       </c>
       <c r="R50" t="n">
-        <v>7377382.643747968</v>
+        <v>7377397.551511872</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -6152,19 +6152,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Espen Quinto-Ashman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Amanda Helander, Astrid Eklund, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Wanyi Ji, Tore Dahlberg, Linnea Backman</t>
+          <t>Espen Quinto-Ashman, Amanda Helander, Astrid Eklund, Elin Lönnberg, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Karl Soler Kinnerbäck, Linnea Backman, Tore Dahlberg, Wanyi Ji</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>95521892</v>
+        <v>95524951</v>
       </c>
       <c r="B51" t="n">
         <v>76909</v>
@@ -6200,14 +6200,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Görjeån, Ö Skraveltjärnen, Lu lm</t>
+          <t>Görjeån, O Skraveltjärnen, Lu lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>731095.7841368329</v>
+        <v>731201.1324956611</v>
       </c>
       <c r="R51" t="n">
-        <v>7377397.551511872</v>
+        <v>7377210.10276178</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
@@ -6264,22 +6264,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Espen Quinto-Ashman</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Espen Quinto-Ashman, Amanda Helander, Astrid Eklund, Elin Lönnberg, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Karl Soler Kinnerbäck, Linnea Backman, Tore Dahlberg, Wanyi Ji</t>
+          <t>Tore Dahlberg, Espen Quinto-Ashman, Karl Soler Kinnerbäck, Amanda Helander, Astrid Eklund, Elin Lönnberg, Wanyi Ji, Iris Elmér, Linnea Backman, Flynn Smedman, Ida Aronsen, Frank Pollari-Karlsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>95524951</v>
+        <v>95524881</v>
       </c>
       <c r="B52" t="n">
-        <v>76909</v>
+        <v>77588</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6292,21 +6292,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6437</v>
+        <v>864</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6316,10 +6316,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>731201.1324956611</v>
+        <v>731294.631420763</v>
       </c>
       <c r="R52" t="n">
-        <v>7377210.10276178</v>
+        <v>7377170.033314993</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6388,10 +6388,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>95524881</v>
+        <v>95524743</v>
       </c>
       <c r="B53" t="n">
-        <v>77588</v>
+        <v>56411</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6404,34 +6404,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>864</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Görjeån, O Skraveltjärnen, Lu lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>731294.631420763</v>
+        <v>731304.4383812491</v>
       </c>
       <c r="R53" t="n">
-        <v>7377170.033314993</v>
+        <v>7377405.260327277</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6458,7 +6463,7 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
@@ -6468,7 +6473,7 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
@@ -6500,10 +6505,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>95524743</v>
+        <v>95526550</v>
       </c>
       <c r="B54" t="n">
-        <v>56411</v>
+        <v>73693</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6516,39 +6521,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Görjeån, O Skraveltjärnen, Lu lm</t>
+          <t>Görjeån, Ö Skravelstjärnen, Lu lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>731304.4383812491</v>
+        <v>731121.5852296054</v>
       </c>
       <c r="R54" t="n">
-        <v>7377405.260327277</v>
+        <v>7377343.810701357</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6605,22 +6605,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Espen Quinto-Ashman, Karl Soler Kinnerbäck, Amanda Helander, Astrid Eklund, Elin Lönnberg, Wanyi Ji, Iris Elmér, Linnea Backman, Flynn Smedman, Ida Aronsen, Frank Pollari-Karlsson</t>
+          <t>Karl Soler Kinnerbäck, Amanda Helander, Astrid Eklund, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Wanyi Ji, Tore Dahlberg, Linnea Backman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>95526550</v>
+        <v>95526597</v>
       </c>
       <c r="B55" t="n">
-        <v>73693</v>
+        <v>76909</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6633,21 +6633,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6657,10 +6657,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>731121.5852296054</v>
+        <v>731072.8137312708</v>
       </c>
       <c r="R55" t="n">
-        <v>7377343.810701357</v>
+        <v>7377325.280919846</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6729,10 +6729,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>95526597</v>
+        <v>95526583</v>
       </c>
       <c r="B56" t="n">
-        <v>76909</v>
+        <v>81236</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6745,21 +6745,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6437</v>
+        <v>1312</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>731072.8137312708</v>
+        <v>731106.0836639035</v>
       </c>
       <c r="R56" t="n">
-        <v>7377325.280919846</v>
+        <v>7377297.892155128</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6841,7 +6841,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>95526583</v>
+        <v>95525738</v>
       </c>
       <c r="B57" t="n">
         <v>81236</v>
@@ -6877,14 +6877,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Görjeån, Ö Skravelstjärnen, Lu lm</t>
+          <t>Görjeån, Ö Skraveltjärnen, Lu lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>731106.0836639035</v>
+        <v>731309.5573388296</v>
       </c>
       <c r="R57" t="n">
-        <v>7377297.892155128</v>
+        <v>7377179.317308596</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
@@ -6941,22 +6941,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Astrid Eklund</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Amanda Helander, Astrid Eklund, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Wanyi Ji, Tore Dahlberg, Linnea Backman</t>
+          <t>Astrid Eklund, Amanda Helander, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Karl Soler Kinnerbäck, Linnea Backman, Tore Dahlberg, Wanyi Ji</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>95525738</v>
+        <v>95526573</v>
       </c>
       <c r="B58" t="n">
-        <v>81236</v>
+        <v>77506</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6969,34 +6969,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Görjeån, Ö Skraveltjärnen, Lu lm</t>
+          <t>Görjeån, Ö Skravelstjärnen, Lu lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>731309.5573388296</v>
+        <v>731136.5032587848</v>
       </c>
       <c r="R58" t="n">
-        <v>7377179.317308596</v>
+        <v>7377324.14390795</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
@@ -7053,22 +7053,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Astrid Eklund</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Astrid Eklund, Amanda Helander, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Karl Soler Kinnerbäck, Linnea Backman, Tore Dahlberg, Wanyi Ji</t>
+          <t>Karl Soler Kinnerbäck, Amanda Helander, Astrid Eklund, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Wanyi Ji, Tore Dahlberg, Linnea Backman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>95526573</v>
+        <v>95526594</v>
       </c>
       <c r="B59" t="n">
-        <v>77506</v>
+        <v>76909</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7081,21 +7081,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7105,10 +7105,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>731136.5032587848</v>
+        <v>731161.0174826731</v>
       </c>
       <c r="R59" t="n">
-        <v>7377324.14390795</v>
+        <v>7377450.418991529</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7177,10 +7177,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>95526594</v>
+        <v>95525722</v>
       </c>
       <c r="B60" t="n">
-        <v>76909</v>
+        <v>81236</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7193,34 +7193,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6437</v>
+        <v>1312</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Görjeån, Ö Skravelstjärnen, Lu lm</t>
+          <t>Görjeån, Ö Skraveltjärnen, Lu lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>731161.0174826731</v>
+        <v>731076.979669224</v>
       </c>
       <c r="R60" t="n">
-        <v>7377450.418991529</v>
+        <v>7377454.285395269</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7277,19 +7277,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Astrid Eklund</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Amanda Helander, Astrid Eklund, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Wanyi Ji, Tore Dahlberg, Linnea Backman</t>
+          <t>Astrid Eklund, Amanda Helander, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Karl Soler Kinnerbäck, Linnea Backman, Tore Dahlberg, Wanyi Ji</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>95525722</v>
+        <v>95526588</v>
       </c>
       <c r="B61" t="n">
         <v>81236</v>
@@ -7323,16 +7323,19 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Görjeån, Ö Skraveltjärnen, Lu lm</t>
+          <t>Görjeån, Ö Skravelstjärnen, Lu lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>731076.979669224</v>
+        <v>731073.8536034208</v>
       </c>
       <c r="R61" t="n">
-        <v>7377454.285395269</v>
+        <v>7377472.519587825</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7383,25 +7386,26 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Astrid Eklund</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Astrid Eklund, Amanda Helander, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Karl Soler Kinnerbäck, Linnea Backman, Tore Dahlberg, Wanyi Ji</t>
+          <t>Karl Soler Kinnerbäck, Amanda Helander, Astrid Eklund, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Wanyi Ji, Tore Dahlberg, Linnea Backman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>95526588</v>
+        <v>95526586</v>
       </c>
       <c r="B62" t="n">
         <v>81236</v>
@@ -7435,19 +7439,16 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Görjeån, Ö Skravelstjärnen, Lu lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>731073.8536034208</v>
+        <v>731144.5189469999</v>
       </c>
       <c r="R62" t="n">
-        <v>7377472.519587825</v>
+        <v>7377276.159952321</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7498,7 +7499,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7517,10 +7517,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>95526586</v>
+        <v>95525713</v>
       </c>
       <c r="B63" t="n">
-        <v>81236</v>
+        <v>95525</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7529,38 +7529,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1312</v>
+        <v>221941</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Görjeån, Ö Skravelstjärnen, Lu lm</t>
+          <t>Görjeån, Ö Skraveltjärnen, Lu lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>731144.5189469999</v>
+        <v>731069.3888418975</v>
       </c>
       <c r="R63" t="n">
-        <v>7377276.159952321</v>
+        <v>7377347.109689075</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7617,22 +7617,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Astrid Eklund</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Amanda Helander, Astrid Eklund, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Wanyi Ji, Tore Dahlberg, Linnea Backman</t>
+          <t>Astrid Eklund, Amanda Helander, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Karl Soler Kinnerbäck, Linnea Backman, Tore Dahlberg, Wanyi Ji</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>95525713</v>
+        <v>95524933</v>
       </c>
       <c r="B64" t="n">
-        <v>95525</v>
+        <v>5113</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7645,34 +7645,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221941</v>
+        <v>100526</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Görjeån, Ö Skraveltjärnen, Lu lm</t>
+          <t>Görjeån, O Skraveltjärnen, Lu lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>731069.3888418975</v>
+        <v>731308.1177102538</v>
       </c>
       <c r="R64" t="n">
-        <v>7377347.109689075</v>
+        <v>7377143.411035416</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7699,7 +7704,7 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
@@ -7709,7 +7714,7 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
@@ -7729,19 +7734,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Astrid Eklund</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Astrid Eklund, Amanda Helander, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Karl Soler Kinnerbäck, Linnea Backman, Tore Dahlberg, Wanyi Ji</t>
+          <t>Tore Dahlberg, Espen Quinto-Ashman, Karl Soler Kinnerbäck, Amanda Helander, Astrid Eklund, Elin Lönnberg, Wanyi Ji, Iris Elmér, Linnea Backman, Flynn Smedman, Ida Aronsen, Frank Pollari-Karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>95524933</v>
+        <v>95524932</v>
       </c>
       <c r="B65" t="n">
         <v>5113</v>
@@ -7786,10 +7791,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>731308.1177102538</v>
+        <v>731087.6039494134</v>
       </c>
       <c r="R65" t="n">
-        <v>7377143.411035416</v>
+        <v>7377326.510659574</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7816,7 +7821,7 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
@@ -7826,7 +7831,7 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
@@ -7858,10 +7863,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>95524932</v>
+        <v>95525724</v>
       </c>
       <c r="B66" t="n">
-        <v>5113</v>
+        <v>81236</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7870,43 +7875,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100526</v>
+        <v>1312</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Görjeån, O Skraveltjärnen, Lu lm</t>
+          <t>Görjeån, Ö Skraveltjärnen, Lu lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>731087.6039494134</v>
+        <v>731096.3050236763</v>
       </c>
       <c r="R66" t="n">
-        <v>7377326.510659574</v>
+        <v>7377352.564195716</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7963,19 +7963,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Astrid Eklund</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Espen Quinto-Ashman, Karl Soler Kinnerbäck, Amanda Helander, Astrid Eklund, Elin Lönnberg, Wanyi Ji, Iris Elmér, Linnea Backman, Flynn Smedman, Ida Aronsen, Frank Pollari-Karlsson</t>
+          <t>Astrid Eklund, Amanda Helander, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Karl Soler Kinnerbäck, Linnea Backman, Tore Dahlberg, Wanyi Ji</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>95525724</v>
+        <v>95525726</v>
       </c>
       <c r="B67" t="n">
         <v>81236</v>
@@ -8015,10 +8015,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>731096.3050236763</v>
+        <v>731141.4169256137</v>
       </c>
       <c r="R67" t="n">
-        <v>7377352.564195716</v>
+        <v>7377260.22102132</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -8087,10 +8087,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>95525726</v>
+        <v>95525740</v>
       </c>
       <c r="B68" t="n">
-        <v>81236</v>
+        <v>77177</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8103,21 +8103,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1312</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8127,10 +8127,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>731141.4169256137</v>
+        <v>731262.9310629906</v>
       </c>
       <c r="R68" t="n">
-        <v>7377260.22102132</v>
+        <v>7377231.729645336</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -8157,7 +8157,7 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
@@ -8199,10 +8199,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>95525740</v>
+        <v>95526548</v>
       </c>
       <c r="B69" t="n">
-        <v>77177</v>
+        <v>73693</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8215,34 +8215,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>353</v>
+        <v>6440</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Görjeån, Ö Skraveltjärnen, Lu lm</t>
+          <t>Görjeån, Ö Skravelstjärnen, Lu lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>731262.9310629906</v>
+        <v>731099.9728887338</v>
       </c>
       <c r="R69" t="n">
-        <v>7377231.729645336</v>
+        <v>7377366.539279395</v>
       </c>
       <c r="S69" t="n">
         <v>20</v>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
@@ -8279,7 +8279,7 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
@@ -8299,19 +8299,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Astrid Eklund</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Astrid Eklund, Amanda Helander, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Karl Soler Kinnerbäck, Linnea Backman, Tore Dahlberg, Wanyi Ji</t>
+          <t>Karl Soler Kinnerbäck, Amanda Helander, Astrid Eklund, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Wanyi Ji, Tore Dahlberg, Linnea Backman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>95526548</v>
+        <v>95526556</v>
       </c>
       <c r="B70" t="n">
         <v>73693</v>
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>731099.9728887338</v>
+        <v>731128.4433704447</v>
       </c>
       <c r="R70" t="n">
-        <v>7377366.539279395</v>
+        <v>7377329.102551386</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -8423,10 +8423,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>95526556</v>
+        <v>95526561</v>
       </c>
       <c r="B71" t="n">
-        <v>73693</v>
+        <v>95525</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8435,25 +8435,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6440</v>
+        <v>221941</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8463,10 +8463,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>731128.4433704447</v>
+        <v>731061.6529647958</v>
       </c>
       <c r="R71" t="n">
-        <v>7377329.102551386</v>
+        <v>7377319.12614882</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -8535,10 +8535,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>95526561</v>
+        <v>95525734</v>
       </c>
       <c r="B72" t="n">
-        <v>95525</v>
+        <v>77588</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8547,38 +8547,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221941</v>
+        <v>864</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Görjeån, Ö Skravelstjärnen, Lu lm</t>
+          <t>Görjeån, Ö Skraveltjärnen, Lu lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>731061.6529647958</v>
+        <v>731253.7563546489</v>
       </c>
       <c r="R72" t="n">
-        <v>7377319.12614882</v>
+        <v>7377167.838395521</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
@@ -8615,7 +8615,7 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
@@ -8635,22 +8635,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Astrid Eklund</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Amanda Helander, Astrid Eklund, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Wanyi Ji, Tore Dahlberg, Linnea Backman</t>
+          <t>Astrid Eklund, Amanda Helander, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Karl Soler Kinnerbäck, Linnea Backman, Tore Dahlberg, Wanyi Ji</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>95525734</v>
+        <v>95525735</v>
       </c>
       <c r="B73" t="n">
-        <v>77588</v>
+        <v>81236</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8663,21 +8663,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8687,10 +8687,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>731253.7563546489</v>
+        <v>731300.8703368135</v>
       </c>
       <c r="R73" t="n">
-        <v>7377167.838395521</v>
+        <v>7377385.262342062</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8759,10 +8759,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>95525735</v>
+        <v>95524901</v>
       </c>
       <c r="B74" t="n">
-        <v>81236</v>
+        <v>89410</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8775,34 +8775,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Görjeån, Ö Skraveltjärnen, Lu lm</t>
+          <t>Görjeån, O Skraveltjärnen, Lu lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>731300.8703368135</v>
+        <v>731254.800941787</v>
       </c>
       <c r="R74" t="n">
-        <v>7377385.262342062</v>
+        <v>7377377.809948722</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8859,22 +8859,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Astrid Eklund</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Astrid Eklund, Amanda Helander, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Karl Soler Kinnerbäck, Linnea Backman, Tore Dahlberg, Wanyi Ji</t>
+          <t>Tore Dahlberg, Espen Quinto-Ashman, Karl Soler Kinnerbäck, Amanda Helander, Astrid Eklund, Elin Lönnberg, Wanyi Ji, Iris Elmér, Linnea Backman, Flynn Smedman, Ida Aronsen, Frank Pollari-Karlsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>95524901</v>
+        <v>95525711</v>
       </c>
       <c r="B75" t="n">
-        <v>89410</v>
+        <v>95525</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8883,38 +8883,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5432</v>
+        <v>221941</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Görjeån, O Skraveltjärnen, Lu lm</t>
+          <t>Görjeån, Ö Skraveltjärnen, Lu lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>731254.800941787</v>
+        <v>731071.190991634</v>
       </c>
       <c r="R75" t="n">
-        <v>7377377.809948722</v>
+        <v>7377359.321373643</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -8941,7 +8941,7 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
@@ -8971,22 +8971,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Astrid Eklund</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Espen Quinto-Ashman, Karl Soler Kinnerbäck, Amanda Helander, Astrid Eklund, Elin Lönnberg, Wanyi Ji, Iris Elmér, Linnea Backman, Flynn Smedman, Ida Aronsen, Frank Pollari-Karlsson</t>
+          <t>Astrid Eklund, Amanda Helander, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Karl Soler Kinnerbäck, Linnea Backman, Tore Dahlberg, Wanyi Ji</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>95525711</v>
+        <v>95526599</v>
       </c>
       <c r="B76" t="n">
-        <v>95525</v>
+        <v>76909</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8995,38 +8995,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221941</v>
+        <v>6437</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Görjeån, Ö Skraveltjärnen, Lu lm</t>
+          <t>Görjeån, Ö Skravelstjärnen, Lu lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>731071.190991634</v>
+        <v>731049.692677488</v>
       </c>
       <c r="R76" t="n">
-        <v>7377359.321373643</v>
+        <v>7377312.904949927</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -9083,22 +9083,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Astrid Eklund</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Astrid Eklund, Amanda Helander, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Karl Soler Kinnerbäck, Linnea Backman, Tore Dahlberg, Wanyi Ji</t>
+          <t>Karl Soler Kinnerbäck, Amanda Helander, Astrid Eklund, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Wanyi Ji, Tore Dahlberg, Linnea Backman</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>95526599</v>
+        <v>95524696</v>
       </c>
       <c r="B77" t="n">
-        <v>76909</v>
+        <v>73693</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9111,34 +9111,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Görjeån, Ö Skravelstjärnen, Lu lm</t>
+          <t>Görjeån, O Skraveltjärnen, Lu lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>731049.692677488</v>
+        <v>731253.6267716239</v>
       </c>
       <c r="R77" t="n">
-        <v>7377312.904949927</v>
+        <v>7377338.711873068</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>
@@ -9165,7 +9165,7 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
@@ -9175,7 +9175,7 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
@@ -9195,22 +9195,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Amanda Helander, Astrid Eklund, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Wanyi Ji, Tore Dahlberg, Linnea Backman</t>
+          <t>Tore Dahlberg, Espen Quinto-Ashman, Karl Soler Kinnerbäck, Amanda Helander, Astrid Eklund, Elin Lönnberg, Wanyi Ji, Iris Elmér, Linnea Backman, Flynn Smedman, Ida Aronsen, Frank Pollari-Karlsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>95524696</v>
+        <v>95524877</v>
       </c>
       <c r="B78" t="n">
-        <v>73693</v>
+        <v>77588</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9223,21 +9223,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6440</v>
+        <v>864</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9247,10 +9247,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>731253.6267716239</v>
+        <v>731245.6466144189</v>
       </c>
       <c r="R78" t="n">
-        <v>7377338.711873068</v>
+        <v>7377405.594547593</v>
       </c>
       <c r="S78" t="n">
         <v>20</v>
@@ -9319,10 +9319,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>95524877</v>
+        <v>95525701</v>
       </c>
       <c r="B79" t="n">
-        <v>77588</v>
+        <v>89557</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9335,34 +9335,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>864</v>
+        <v>1588</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Görjeån, O Skraveltjärnen, Lu lm</t>
+          <t>Görjeån, Ö Skraveltjärnen, Lu lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>731245.6466144189</v>
+        <v>731129.1372095407</v>
       </c>
       <c r="R79" t="n">
-        <v>7377405.594547593</v>
+        <v>7377436.912044343</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -9389,7 +9389,7 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
@@ -9419,22 +9419,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Astrid Eklund</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Espen Quinto-Ashman, Karl Soler Kinnerbäck, Amanda Helander, Astrid Eklund, Elin Lönnberg, Wanyi Ji, Iris Elmér, Linnea Backman, Flynn Smedman, Ida Aronsen, Frank Pollari-Karlsson</t>
+          <t>Astrid Eklund, Amanda Helander, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Karl Soler Kinnerbäck, Linnea Backman, Tore Dahlberg, Wanyi Ji</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>95525701</v>
+        <v>95526570</v>
       </c>
       <c r="B80" t="n">
-        <v>89557</v>
+        <v>77588</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9447,34 +9447,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1588</v>
+        <v>864</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Görjeån, Ö Skraveltjärnen, Lu lm</t>
+          <t>Görjeån, Ö Skravelstjärnen, Lu lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>731129.1372095407</v>
+        <v>731144.1917574101</v>
       </c>
       <c r="R80" t="n">
-        <v>7377436.912044343</v>
+        <v>7377299.45296608</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -9531,22 +9531,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Astrid Eklund</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Astrid Eklund, Amanda Helander, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Karl Soler Kinnerbäck, Linnea Backman, Tore Dahlberg, Wanyi Ji</t>
+          <t>Karl Soler Kinnerbäck, Amanda Helander, Astrid Eklund, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Wanyi Ji, Tore Dahlberg, Linnea Backman</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>95526570</v>
+        <v>95526606</v>
       </c>
       <c r="B81" t="n">
-        <v>77588</v>
+        <v>101680</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9555,25 +9555,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>864</v>
+        <v>222412</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9583,10 +9583,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>731144.1917574101</v>
+        <v>731316.7804994041</v>
       </c>
       <c r="R81" t="n">
-        <v>7377299.45296608</v>
+        <v>7377150.565531123</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -9613,7 +9613,7 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
@@ -9623,7 +9623,7 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
@@ -9655,10 +9655,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>95526606</v>
+        <v>95524718</v>
       </c>
       <c r="B82" t="n">
-        <v>101680</v>
+        <v>56395</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9667,38 +9667,43 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>222412</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Görjeån, Ö Skravelstjärnen, Lu lm</t>
+          <t>Görjeån, O Skraveltjärnen, Lu lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>731316.7804994041</v>
+        <v>731310.4877543944</v>
       </c>
       <c r="R82" t="n">
-        <v>7377150.565531123</v>
+        <v>7377337.412717641</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>
@@ -9755,22 +9760,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Amanda Helander, Astrid Eklund, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Wanyi Ji, Tore Dahlberg, Linnea Backman</t>
+          <t>Tore Dahlberg, Espen Quinto-Ashman, Karl Soler Kinnerbäck, Amanda Helander, Astrid Eklund, Elin Lönnberg, Wanyi Ji, Iris Elmér, Linnea Backman, Flynn Smedman, Ida Aronsen, Frank Pollari-Karlsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>95524718</v>
+        <v>95524781</v>
       </c>
       <c r="B83" t="n">
-        <v>56395</v>
+        <v>95525</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9779,43 +9784,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Görjeån, O Skraveltjärnen, Lu lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>731310.4877543944</v>
+        <v>731296.9594142459</v>
       </c>
       <c r="R83" t="n">
-        <v>7377337.412717641</v>
+        <v>7377316.183236159</v>
       </c>
       <c r="S83" t="n">
         <v>20</v>
@@ -9884,10 +9884,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>95524781</v>
+        <v>95525725</v>
       </c>
       <c r="B84" t="n">
-        <v>95525</v>
+        <v>81236</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9896,38 +9896,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221941</v>
+        <v>1312</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Görjeån, O Skraveltjärnen, Lu lm</t>
+          <t>Görjeån, Ö Skraveltjärnen, Lu lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>731296.9594142459</v>
+        <v>731102.6278793053</v>
       </c>
       <c r="R84" t="n">
-        <v>7377316.183236159</v>
+        <v>7377329.770242247</v>
       </c>
       <c r="S84" t="n">
         <v>20</v>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
@@ -9984,22 +9984,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Astrid Eklund</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Espen Quinto-Ashman, Karl Soler Kinnerbäck, Amanda Helander, Astrid Eklund, Elin Lönnberg, Wanyi Ji, Iris Elmér, Linnea Backman, Flynn Smedman, Ida Aronsen, Frank Pollari-Karlsson</t>
+          <t>Astrid Eklund, Amanda Helander, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Karl Soler Kinnerbäck, Linnea Backman, Tore Dahlberg, Wanyi Ji</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>95525725</v>
+        <v>95525715</v>
       </c>
       <c r="B85" t="n">
-        <v>81236</v>
+        <v>95525</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10008,25 +10008,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1312</v>
+        <v>221941</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10036,10 +10036,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>731102.6278793053</v>
+        <v>731145.5816548612</v>
       </c>
       <c r="R85" t="n">
-        <v>7377329.770242247</v>
+        <v>7377263.381920612</v>
       </c>
       <c r="S85" t="n">
         <v>20</v>
@@ -10108,10 +10108,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>95525715</v>
+        <v>95526581</v>
       </c>
       <c r="B86" t="n">
-        <v>95525</v>
+        <v>81236</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10120,38 +10120,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221941</v>
+        <v>1312</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Görjeån, Ö Skraveltjärnen, Lu lm</t>
+          <t>Görjeån, Ö Skravelstjärnen, Lu lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>731145.5816548612</v>
+        <v>731141.8978569109</v>
       </c>
       <c r="R86" t="n">
-        <v>7377263.381920612</v>
+        <v>7377317.355333193</v>
       </c>
       <c r="S86" t="n">
         <v>20</v>
@@ -10208,22 +10208,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Astrid Eklund</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Astrid Eklund, Amanda Helander, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Karl Soler Kinnerbäck, Linnea Backman, Tore Dahlberg, Wanyi Ji</t>
+          <t>Karl Soler Kinnerbäck, Amanda Helander, Astrid Eklund, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Wanyi Ji, Tore Dahlberg, Linnea Backman</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>95526581</v>
+        <v>95526542</v>
       </c>
       <c r="B87" t="n">
-        <v>81236</v>
+        <v>5135</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10232,38 +10232,47 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1312</v>
+        <v>105930</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Görjeån, Ö Skravelstjärnen, Lu lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>731141.8978569109</v>
+        <v>731122.0068365773</v>
       </c>
       <c r="R87" t="n">
-        <v>7377317.355333193</v>
+        <v>7377300.020414264</v>
       </c>
       <c r="S87" t="n">
         <v>20</v>
@@ -10314,6 +10323,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -10332,10 +10342,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>95526542</v>
+        <v>95526589</v>
       </c>
       <c r="B88" t="n">
-        <v>5135</v>
+        <v>76486</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10344,36 +10354,30 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>105930</v>
+        <v>6487</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -10381,10 +10385,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>731122.0068365773</v>
+        <v>731162.2166363262</v>
       </c>
       <c r="R88" t="n">
-        <v>7377300.020414264</v>
+        <v>7377450.518736145</v>
       </c>
       <c r="S88" t="n">
         <v>20</v>
@@ -10454,7 +10458,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>95526589</v>
+        <v>95521891</v>
       </c>
       <c r="B89" t="n">
         <v>76486</v>
@@ -10493,14 +10497,14 @@
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Görjeån, Ö Skravelstjärnen, Lu lm</t>
+          <t>Görjeån, Ö Skraveltjärnen, Lu lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>731162.2166363262</v>
+        <v>731095.7841368329</v>
       </c>
       <c r="R89" t="n">
-        <v>7377450.518736145</v>
+        <v>7377397.551511872</v>
       </c>
       <c r="S89" t="n">
         <v>20</v>
@@ -10558,19 +10562,19 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Espen Quinto-Ashman</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Amanda Helander, Astrid Eklund, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Wanyi Ji, Tore Dahlberg, Linnea Backman</t>
+          <t>Espen Quinto-Ashman, Amanda Helander, Astrid Eklund, Elin Lönnberg, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Karl Soler Kinnerbäck, Linnea Backman, Tore Dahlberg, Wanyi Ji</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>95521891</v>
+        <v>95526591</v>
       </c>
       <c r="B90" t="n">
         <v>76486</v>
@@ -10609,14 +10613,14 @@
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Görjeån, Ö Skraveltjärnen, Lu lm</t>
+          <t>Görjeån, Ö Skravelstjärnen, Lu lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>731095.7841368329</v>
+        <v>731095.5654570702</v>
       </c>
       <c r="R90" t="n">
-        <v>7377397.551511872</v>
+        <v>7377327.574721696</v>
       </c>
       <c r="S90" t="n">
         <v>20</v>
@@ -10674,22 +10678,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Espen Quinto-Ashman</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Espen Quinto-Ashman, Amanda Helander, Astrid Eklund, Elin Lönnberg, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Karl Soler Kinnerbäck, Linnea Backman, Tore Dahlberg, Wanyi Ji</t>
+          <t>Karl Soler Kinnerbäck, Amanda Helander, Astrid Eklund, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Wanyi Ji, Tore Dahlberg, Linnea Backman</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>95526591</v>
+        <v>96409774</v>
       </c>
       <c r="B91" t="n">
-        <v>76486</v>
+        <v>89545</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10698,44 +10702,52 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6487</v>
+        <v>1503</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Görjeån, Ö Skravelstjärnen, Lu lm</t>
+          <t>Görjeån, Ö skraveltjärnen, Lu lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>731095.5654570702</v>
+        <v>731282.6556903012</v>
       </c>
       <c r="R91" t="n">
-        <v>7377327.574721696</v>
+        <v>7377251.062608211</v>
       </c>
       <c r="S91" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10759,7 +10771,7 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
@@ -10769,7 +10781,7 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
@@ -10783,7 +10795,11 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -10795,17 +10811,17 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Amanda Helander, Astrid Eklund, Elin Lönnberg, Espen Quinto-Ashman, Flynn Smedman, Frank Pollari-Karlsson, Ida Aronsen, Iris Elmér, Wanyi Ji, Tore Dahlberg, Linnea Backman</t>
+          <t>Karl Soler Kinnerbäck, Tore Dahlberg, Astrid Eklund, Iris Elmér, Ida Aronsen, Frank Pollari-Karlsson, Linnea Backman, Wanyi Ji, Amanda Helander, Flynn Smedman, Espen Quinto-Ashman, Elin Lönnberg</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>96409774</v>
+        <v>96409760</v>
       </c>
       <c r="B92" t="n">
-        <v>89545</v>
+        <v>73698</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10814,52 +10830,44 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1503</v>
+        <v>1467</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Görjeån, Ö skraveltjärnen, Lu lm</t>
+          <t>Görjeån, Ö Skraveltjärnen, Lu lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>731282.6556903012</v>
+        <v>731325.2836060632</v>
       </c>
       <c r="R92" t="n">
-        <v>7377251.062608211</v>
+        <v>7377193.493076357</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10907,11 +10915,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10930,10 +10934,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>96409760</v>
+        <v>96965438</v>
       </c>
       <c r="B93" t="n">
-        <v>73698</v>
+        <v>76486</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10946,21 +10950,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1467</v>
+        <v>6487</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10969,17 +10973,17 @@
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Görjeån, Ö Skraveltjärnen, Lu lm</t>
+          <t>Görjeån, Lu lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>731325.2836060632</v>
+        <v>731075.7633380449</v>
       </c>
       <c r="R93" t="n">
-        <v>7377193.493076357</v>
+        <v>7377391.46416633</v>
       </c>
       <c r="S93" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11003,7 +11007,7 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">
@@ -11013,7 +11017,7 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
@@ -11039,17 +11043,17 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Tore Dahlberg, Astrid Eklund, Iris Elmér, Ida Aronsen, Frank Pollari-Karlsson, Linnea Backman, Wanyi Ji, Amanda Helander, Flynn Smedman, Espen Quinto-Ashman, Elin Lönnberg</t>
+          <t>Karl Soler Kinnerbäck, Tore Dahlberg, Iris Elmér, Linnea Backman, Astrid Eklund, Frank Pollari-Karlsson, Amanda Helander, Espen Quinto-Ashman, Elin Lönnberg, Flynn Smedman, Ida Aronsen, Wanyi Ji</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>96965438</v>
+        <v>98309534</v>
       </c>
       <c r="B94" t="n">
-        <v>76486</v>
+        <v>77177</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11062,37 +11066,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6487</v>
+        <v>353</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Görjeån, Lu lm</t>
+          <t>Kullmyrbäcken-Kåtamyrbäcken-Gör, Lu lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>731075.7633380449</v>
+        <v>731318.3234785929</v>
       </c>
       <c r="R94" t="n">
-        <v>7377391.46416633</v>
+        <v>7377204.574412997</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11119,7 +11120,7 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2021-08-06</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
@@ -11129,7 +11130,7 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2021-08-06</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
@@ -11143,29 +11144,28 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Tore Dahlberg, Iris Elmér, Linnea Backman, Astrid Eklund, Frank Pollari-Karlsson, Amanda Helander, Espen Quinto-Ashman, Elin Lönnberg, Flynn Smedman, Ida Aronsen, Wanyi Ji</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>98309534</v>
+        <v>98309537</v>
       </c>
       <c r="B95" t="n">
-        <v>77177</v>
+        <v>88806</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11174,25 +11174,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>353</v>
+        <v>5685</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11202,10 +11202,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>731318.3234785929</v>
+        <v>731322.3542495666</v>
       </c>
       <c r="R95" t="n">
-        <v>7377204.574412997</v>
+        <v>7377204.50779463</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11274,10 +11274,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>98309537</v>
+        <v>98309523</v>
       </c>
       <c r="B96" t="n">
-        <v>88806</v>
+        <v>78098</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11286,25 +11286,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5685</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11314,10 +11314,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>731322.3542495666</v>
+        <v>731281.7394584249</v>
       </c>
       <c r="R96" t="n">
-        <v>7377204.50779463</v>
+        <v>7377170.166794272</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11383,118 +11383,6 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>98309523</v>
-      </c>
-      <c r="B97" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E97" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>Kullmyrbäcken-Kåtamyrbäcken-Gör, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q97" t="n">
-        <v>731281.7394584249</v>
-      </c>
-      <c r="R97" t="n">
-        <v>7377170.166794272</v>
-      </c>
-      <c r="S97" t="n">
-        <v>10</v>
-      </c>
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>Jokkmokk</t>
-        </is>
-      </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W97" t="inlineStr">
-        <is>
-          <t>Jokkmokk</t>
-        </is>
-      </c>
-      <c r="Y97" t="inlineStr">
-        <is>
-          <t>2021-08-06</t>
-        </is>
-      </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>2021-08-06</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT97" t="inlineStr"/>
-      <c r="AW97" t="inlineStr">
-        <is>
-          <t>Sture Westerberg</t>
-        </is>
-      </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AY97" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
